--- a/data_output/MSP.xlsx
+++ b/data_output/MSP.xlsx
@@ -396,16 +396,16 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>0.002978444109810175</v>
+        <v>0.00544308942999945</v>
       </c>
       <c r="D2">
-        <v>0.00182914883631696</v>
+        <v>0.002323821897461308</v>
       </c>
       <c r="E2">
-        <v>2.855105501734859e-05</v>
+        <v>2.98290977949473E-05</v>
       </c>
       <c r="F2">
-        <v>0.001955594952039983</v>
+        <v>0.002544238232701615</v>
       </c>
     </row>
     <row r="3">
@@ -418,16 +418,16 @@
         <v>150</v>
       </c>
       <c r="C3">
-        <v>0.0004064854781701174</v>
+        <v>0.0004637687859314783</v>
       </c>
       <c r="D3">
-        <v>0.001085490999319872</v>
+        <v>0.001489536180495347</v>
       </c>
       <c r="E3">
-        <v>4.073873559873901e-05</v>
+        <v>6.056573460343597E-05</v>
       </c>
       <c r="F3">
-        <v>0.0004350346360313801</v>
+        <v>0.0006050899705159547</v>
       </c>
     </row>
     <row r="4">
@@ -440,16 +440,16 @@
         <v>250</v>
       </c>
       <c r="C4">
-        <v>0.004622298194472249</v>
+        <v>0.01305276098725969</v>
       </c>
       <c r="D4">
-        <v>0.0004030800961405823</v>
+        <v>0.0004913829237989317</v>
       </c>
       <c r="E4">
-        <v>5.280485872811138e-05</v>
+        <v>5.456796218466981E-05</v>
       </c>
       <c r="F4">
-        <v>0.0004909038158045692</v>
+        <v>0.0005883081932810535</v>
       </c>
     </row>
     <row r="5">
@@ -462,16 +462,16 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>2.857297827538873e-05</v>
+        <v>0.000457419685534191</v>
       </c>
       <c r="D5">
-        <v>0.0001242545427417546</v>
+        <v>0.0003061131354037466</v>
       </c>
       <c r="E5">
-        <v>4.471051358278195e-06</v>
+        <v>5.404587795393711E-05</v>
       </c>
       <c r="F5">
-        <v>4.516419345040797e-05</v>
+        <v>0.0003092759622378577</v>
       </c>
     </row>
     <row r="6">
@@ -484,16 +484,16 @@
         <v>150</v>
       </c>
       <c r="C6">
-        <v>3.127022891665292e-07</v>
+        <v>6.627281930607034E-05</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4.252959812191807E-05</v>
       </c>
       <c r="E6">
-        <v>5.2699126517684e-07</v>
+        <v>6.344973574223151E-06</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5.652902033330686E-05</v>
       </c>
     </row>
     <row r="7">
@@ -506,16 +506,10 @@
         <v>270</v>
       </c>
       <c r="C7">
-        <v>3.206964961804261e-06</v>
-      </c>
-      <c r="D7">
-        <v>2.397513848060834e-07</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
+        <v>8.519671301442315E-06</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>8.519671301442315E-06</v>
       </c>
     </row>
     <row r="8">
@@ -528,16 +522,16 @@
         <v>20</v>
       </c>
       <c r="C8">
-        <v>0.005209872724620913</v>
+        <v>0.01108071467301234</v>
       </c>
       <c r="D8">
-        <v>0.001571667784911813</v>
+        <v>0.002128336682762268</v>
       </c>
       <c r="E8">
-        <v>7.91785825418965e-05</v>
+        <v>8.291055122192256E-05</v>
       </c>
       <c r="F8">
-        <v>0.004808354863048059</v>
+        <v>0.009362165287865015</v>
       </c>
     </row>
     <row r="9">
@@ -550,16 +544,16 @@
         <v>150</v>
       </c>
       <c r="C9">
-        <v>0.005827114304218977</v>
+        <v>0.02257277366771324</v>
       </c>
       <c r="D9">
-        <v>0.001734705471846837</v>
+        <v>0.002424395486173082</v>
       </c>
       <c r="E9">
-        <v>2.715658361669913e-05</v>
+        <v>3.140112489269784E-05</v>
       </c>
       <c r="F9">
-        <v>0.001859773353383564</v>
+        <v>0.002691420712844131</v>
       </c>
     </row>
     <row r="10">
@@ -572,16 +566,16 @@
         <v>270</v>
       </c>
       <c r="C10">
-        <v>0.005502866884386694</v>
+        <v>0.01294905868490636</v>
       </c>
       <c r="D10">
-        <v>0.001701825646454912</v>
+        <v>0.002358091922445714</v>
       </c>
       <c r="E10">
-        <v>1.612405980483786e-05</v>
+        <v>2.120012057230263E-05</v>
       </c>
       <c r="F10">
-        <v>0.001739895593077417</v>
+        <v>0.002530868857130161</v>
       </c>
     </row>
   </sheetData>
